--- a/seed_data/excel/Boztepe_Repayment_Schedule_84_Instalments.xlsx
+++ b/seed_data/excel/Boztepe_Repayment_Schedule_84_Instalments.xlsx
@@ -82,7 +82,7 @@
     <t xml:space="preserve">generated_at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T18:22:15+00:00</t>
+    <t xml:space="preserve">2026-10-12T13:12:20+00:00</t>
   </si>
   <si>
     <t xml:space="preserve">ledger_schema_version</t>
